--- a/fixtures/eval/questionnaire_eval.xlsx
+++ b/fixtures/eval/questionnaire_eval.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -697,6 +697,54 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ADV-01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Are encryption keys stored in a hardware security module (HSM)?</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ADV-02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Are backups stored off-site at a geographically separate facility?</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ADV-03</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Are passwords stored using a salted, one-way cryptographic hashing algorithm?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ADV-04</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Are user access reviews automated through an identity governance and administration (IGA) platform?</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
